--- a/Test-Scenario/Test_Scenarios.xlsx
+++ b/Test-Scenario/Test_Scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Microsoft\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530B56EF-ABBA-4178-B0F6-97DFF2D57B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11A448D-02B2-4F98-B559-D7B7E860EE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{776C9A32-17FA-4198-9478-22585F8DA60D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="51">
   <si>
     <t>Module</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Verify product sorting by price (low to high)</t>
   </si>
   <si>
-    <t>Security (basic)</t>
-  </si>
-  <si>
     <t>Verify password field masks entered text</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
   </si>
   <si>
     <t>Verify checkout with invalid personal information</t>
-  </si>
-  <si>
-    <t>Empty fields</t>
   </si>
   <si>
     <t>Coverage</t>
@@ -609,27 +603,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -641,15 +635,15 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -664,12 +658,12 @@
         <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
@@ -681,21 +675,21 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -704,12 +698,12 @@
         <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -721,15 +715,15 @@
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
@@ -741,18 +735,18 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -764,15 +758,15 @@
         <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -784,15 +778,15 @@
         <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -804,12 +798,12 @@
         <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>4</v>
@@ -824,12 +818,12 @@
         <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>4</v>
@@ -844,12 +838,12 @@
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -861,15 +855,15 @@
         <v>3</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -881,21 +875,21 @@
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>3</v>
@@ -904,12 +898,12 @@
         <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>5</v>
@@ -921,30 +915,30 @@
         <v>3</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
